--- a/AIVIA_Design/L1_KG3_Artifact_Layer_Registry.xlsx
+++ b/AIVIA_Design/L1_KG3_Artifact_Layer_Registry.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT v0.1 — companion registry authored 2026-09-05 from the RATIFIED KG Layer 3 section of the AIVIA Design Document (protocol step 2). The doc is the authority; any doc change updates this registry in the same breath. All build deferred by the phase ruling.</t>
+          <t>DRAFT v0.1 — companion registry authored 2026-09-05 from the RATIFIED KG Layer 3 section of the AISQL Design Document (protocol step 2). The doc is the authority; any doc change updates this registry in the same breath. All build deferred by the phase ruling.</t>
         </is>
       </c>
     </row>
